--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/MASSACHUSETTS_2013.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/MASSACHUSETTS_2013.xlsx
@@ -4794,7 +4794,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C247">
